--- a/Graph_22.4.25.xlsx
+++ b/Graph_22.4.25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ResearchProject\Sorowar Sir\Causes of Deaths\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA4A487-4015-4F53-9B5F-C718D5C87376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42938CA-C106-449E-BDF8-E4EFB14CEC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{D59E1812-00E2-46C2-B4ED-CEBFB390F202}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{D59E1812-00E2-46C2-B4ED-CEBFB390F202}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>Jan</t>
   </si>
@@ -189,22 +189,31 @@
     <t>Known disease</t>
   </si>
   <si>
-    <t>Unknown disease</t>
-  </si>
-  <si>
-    <t>Known Cause</t>
-  </si>
-  <si>
-    <t>Unknown Cause</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Causes of death</t>
   </si>
   <si>
     <t>Numbers</t>
+  </si>
+  <si>
+    <t>Lung failure</t>
+  </si>
+  <si>
+    <t>Accidents and Injuries</t>
+  </si>
+  <si>
+    <t>Cancer (Malignant Diseases)</t>
+  </si>
+  <si>
+    <t>Cardiovascular Diseases</t>
+  </si>
+  <si>
+    <t>Chronic Health Conditions</t>
+  </si>
+  <si>
+    <t>Respiratory Diseases</t>
+  </si>
+  <si>
+    <t>Other Health Conditions</t>
   </si>
 </sst>
 </file>
@@ -967,37 +976,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>87</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>93</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>85</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>96</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>106</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>87</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>118</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>129</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1141,37 +1150,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>115</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>84</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>74</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>96</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>72</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>65</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>105</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1315,37 +1324,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>64</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>72</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>79</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>89</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>109</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1489,37 +1498,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>48</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>55</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>82</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>81</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>83</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1663,37 +1672,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>51</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>55</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>74</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>98</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>63</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>55</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>91</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1837,37 +1846,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>54</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>105</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>102</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2011,37 +2020,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>66</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>71</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>81</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>64</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>78</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>67</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>146</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2185,37 +2194,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>46</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>59</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>94</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>90</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>75</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>153</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2359,37 +2368,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>78</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>49</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>58</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>77</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>83</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>130</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2533,37 +2542,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>59</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>69</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>98</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>73</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>66</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>121</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2707,37 +2716,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>71</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>83</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>108</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>122</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>97</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2881,37 +2890,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>90</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>69</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>57</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>64</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>87</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>104</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>95</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>119</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>120</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>99</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3348,9 +3357,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet2!$A$2:$A$36</c:f>
+              <c:f>Sheet2!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>Rail accident</c:v>
                 </c:pt>
@@ -3406,7 +3415,7 @@
                   <c:v>Neonatal death</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>Lung Failure</c:v>
+                  <c:v>Lung failure</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>Road Accident</c:v>
@@ -3452,19 +3461,16 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>Stroke</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Unknown</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$2:$B$36</c:f>
+              <c:f>Sheet2!$B$2:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3553,7 +3559,7 @@
                   <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>282</c:v>
+                  <c:v>281</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>297</c:v>
@@ -3566,9 +3572,6 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>2833</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3896,305 +3899,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
-              <a:t>Distribution of causes: Known vs Unknown</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-D148-48F2-9093-63FAAA0C380F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-D148-48F2-9093-63FAAA0C380F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$49:$A$50</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Known Cause</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Unknown Cause</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$49:$B$50</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>6333</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4138</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1A6B-495A-8861-E0A8A46518F8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Types of death by known causes</a:t>
+              <a:t>Types of deaths by causes</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4418,22 +4124,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Accident</c:v>
+                  <c:v>Accidents and Injuries</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Cancer</c:v>
+                  <c:v>Cancer (Malignant Diseases)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Cardiovascular disease</c:v>
+                  <c:v>Cardiovascular Diseases</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Chronic Disease</c:v>
+                  <c:v>Chronic Health Conditions</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Lung disease</c:v>
+                  <c:v>Respiratory Diseases</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Other</c:v>
+                  <c:v>Other Health Conditions</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4457,7 +4163,7 @@
                   <c:v>404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>691</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1035</c:v>
@@ -4652,46 +4358,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -5701,525 +5367,6 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6824,52 +5971,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EEE587E-DCC5-4644-385E-7CDBB353105D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6888,7 +5999,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7235,7 +6346,7 @@
         <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -7243,44 +6354,43 @@
         <v>2011</v>
       </c>
       <c r="B2">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D2">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E2">
+        <v>31</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>37</v>
+      </c>
+      <c r="I2">
+        <v>26</v>
+      </c>
+      <c r="J2">
         <v>48</v>
       </c>
-      <c r="F2">
-        <v>51</v>
-      </c>
-      <c r="G2">
-        <v>40</v>
-      </c>
-      <c r="H2">
-        <v>66</v>
-      </c>
-      <c r="I2">
-        <v>46</v>
-      </c>
-      <c r="J2">
-        <v>78</v>
-      </c>
       <c r="K2">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L2">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="N2">
-        <f>SUM(B2:M2)</f>
-        <v>815</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -7288,44 +6398,43 @@
         <v>2012</v>
       </c>
       <c r="B3">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C3">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="K3">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="L3">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N12" si="0">SUM(B3:M3)</f>
-        <v>763</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -7333,44 +6442,43 @@
         <v>2013</v>
       </c>
       <c r="B4">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="H4">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="I4">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="J4">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K4">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L4">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="M4">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="N4">
-        <f t="shared" si="0"/>
-        <v>754</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -7378,44 +6486,43 @@
         <v>2014</v>
       </c>
       <c r="B5">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C5">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="H5">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="K5">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L5">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="M5">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="N5">
-        <f t="shared" si="0"/>
-        <v>845</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -7423,44 +6530,43 @@
         <v>2015</v>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E6">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>46</v>
+      </c>
+      <c r="G6">
         <v>59</v>
       </c>
-      <c r="F6">
-        <v>69</v>
-      </c>
-      <c r="G6">
-        <v>81</v>
-      </c>
       <c r="H6">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="J6">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="K6">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L6">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="N6">
-        <f t="shared" si="0"/>
-        <v>877</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -7468,44 +6574,43 @@
         <v>2016</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E7">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="I7">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="J7">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="K7">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="L7">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="M7">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="N7">
-        <f t="shared" si="0"/>
-        <v>903</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -7513,44 +6618,43 @@
         <v>2017</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="D8">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="E8">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F8">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="H8">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="J8">
+        <v>34</v>
+      </c>
+      <c r="K8">
         <v>58</v>
       </c>
-      <c r="K8">
-        <v>98</v>
-      </c>
       <c r="L8">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M8">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="N8">
-        <f t="shared" si="0"/>
-        <v>1033</v>
+        <v>661</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -7558,44 +6662,43 @@
         <v>2018</v>
       </c>
       <c r="B9">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H9">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="I9">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="J9">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="L9">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="M9">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="N9">
-        <f t="shared" si="0"/>
-        <v>947</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -7603,44 +6706,43 @@
         <v>2019</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="D10">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E10">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F10">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="G10">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I10">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="J10">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="K10">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L10">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="M10">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="N10">
-        <f t="shared" si="0"/>
-        <v>1068</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -7648,44 +6750,43 @@
         <v>2020</v>
       </c>
       <c r="B11">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="C11">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E11">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F11">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G11">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="H11">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="I11">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="J11">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="K11">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="L11">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="M11">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="N11">
-        <f t="shared" si="0"/>
-        <v>1205</v>
+        <v>731</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -7693,101 +6794,87 @@
         <v>2021</v>
       </c>
       <c r="B12">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="C12">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="D12">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E12">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="F12">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="G12">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="H12">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="I12">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="J12">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="K12">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="L12">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="M12">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="N12">
-        <f t="shared" si="0"/>
-        <v>1270</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B13">
-        <f>SUM(B2:B12)</f>
-        <v>1062</v>
+        <v>545</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:N13" si="1">SUM(C2:C12)</f>
-        <v>922</v>
+        <v>546</v>
       </c>
       <c r="D13">
-        <f t="shared" si="1"/>
-        <v>870</v>
+        <v>514</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
-        <v>732</v>
+        <v>461</v>
       </c>
       <c r="F13">
-        <f t="shared" si="1"/>
-        <v>749</v>
+        <v>440</v>
       </c>
       <c r="G13">
-        <f t="shared" si="1"/>
-        <v>792</v>
+        <v>487</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
-        <v>883</v>
+        <v>550</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
-        <v>846</v>
+        <v>520</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
-        <v>847</v>
+        <v>558</v>
       </c>
       <c r="K13">
-        <f t="shared" si="1"/>
-        <v>815</v>
+        <v>514</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
-        <v>958</v>
+        <v>590</v>
       </c>
       <c r="M13">
-        <f t="shared" si="1"/>
-        <v>1004</v>
+        <v>607</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
-        <v>10480</v>
+        <v>6332</v>
       </c>
     </row>
   </sheetData>
@@ -7798,15 +6885,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AE742B-6ADF-44B8-9792-98B0806A200F}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7955,7 +7042,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B20">
         <v>63</v>
@@ -8046,7 +7133,7 @@
         <v>21</v>
       </c>
       <c r="B31">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -8079,14 +7166,6 @@
       </c>
       <c r="B35">
         <v>2833</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36">
-        <v>4138</v>
       </c>
     </row>
   </sheetData>
@@ -8102,11 +7181,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3308E310-C61C-4A2C-96ED-391E0552076A}">
-  <dimension ref="A2:J50"/>
+  <dimension ref="A2:J46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" customWidth="1"/>
     <col min="4" max="4" width="22.85546875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
@@ -8564,7 +7643,7 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C41">
         <v>461</v>
@@ -8573,7 +7652,7 @@
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>662</v>
@@ -8582,7 +7661,7 @@
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C43">
         <v>3080</v>
@@ -8591,7 +7670,7 @@
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>404</v>
@@ -8600,46 +7679,19 @@
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="C45">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C46">
         <v>1035</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47">
-        <v>4138</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49">
-        <v>6333</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50">
-        <v>4138</v>
       </c>
     </row>
   </sheetData>
